--- a/Articoli/Settimana fiscale/14-Dividendi e compensi/EsempioNumerico.xlsx
+++ b/Articoli/Settimana fiscale/14-Dividendi e compensi/EsempioNumerico.xlsx
@@ -1540,8 +1540,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010049B2E99503D3AD4DA2231F0D240043DD" ma:contentTypeVersion="18" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="57b8045e8abefa85dedc7991371a38b2">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77a3f60d-3740-4b8f-aea2-18b203205ead" xmlns:ns3="6c014026-a0ef-45dc-9ca9-ac355db24e99" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5ecd2ee382a35af39c71524ba84a011" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010049B2E99503D3AD4DA2231F0D240043DD" ma:contentTypeVersion="19" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="5d22b860b2d7b05646517e191754a185">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77a3f60d-3740-4b8f-aea2-18b203205ead" xmlns:ns3="6c014026-a0ef-45dc-9ca9-ac355db24e99" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c3ef981538194d0481c402a9a66d521d" ns2:_="" ns3:_="">
     <xsd:import namespace="77a3f60d-3740-4b8f-aea2-18b203205ead"/>
     <xsd:import namespace="6c014026-a0ef-45dc-9ca9-ac355db24e99"/>
     <xsd:element name="properties">
@@ -1567,6 +1567,7 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1651,6 +1652,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -1814,20 +1820,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18CE396C-9BA8-4A07-A47F-939CE63921A5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77a3f60d-3740-4b8f-aea2-18b203205ead"/>
-    <ds:schemaRef ds:uri="6c014026-a0ef-45dc-9ca9-ac355db24e99"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95696172-8503-4A91-80AE-DF154AD52DB4}"/>
 </file>